--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484132_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484132_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8725</v>
+        <v>7.8521</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8224</v>
+        <v>8.026400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0501</v>
+        <v>-0.1743</v>
       </c>
       <c r="G2" t="n">
         <v>3.4324</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.144</v>
+        <v>-0.1644</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6518</v>
+        <v>-0.4477</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5077</v>
+        <v>0.2833</v>
       </c>
       <c r="V2" t="n">
         <v>6.3696</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9893</v>
+        <v>5.9878</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1847</v>
+        <v>5.043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8046</v>
+        <v>0.9449</v>
       </c>
       <c r="G3" t="n">
         <v>4.8916</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0425</v>
+        <v>0.0411</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3288</v>
+        <v>0.1871</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2863</v>
+        <v>-0.146</v>
       </c>
       <c r="V3" t="n">
         <v>-0.532</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4012</v>
+        <v>0.6716</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7046</v>
+        <v>-0.6026</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1058</v>
+        <v>1.2742</v>
       </c>
       <c r="G4" t="n">
         <v>0.4023</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1995</v>
+        <v>0.0709</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3004</v>
+        <v>-0.1983</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1009</v>
+        <v>0.2692</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1766</v>
+        <v>-0.1078</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8511</v>
+        <v>4.3769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6745</v>
+        <v>-4.4846</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8309</v>
+        <v>-0.899</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8309</v>
+        <v>-0.9678</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0687</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8309</v>
+        <v>3.755</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8309</v>
+        <v>1.7042</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.0508</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-4.654</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-2.6719</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.9821</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-1.3887</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3604</v>
+        <v>-0.3358</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3604</v>
+        <v>0.2722</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.608</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2777</v>
+        <v>0.532</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6032</v>
+        <v>1.7384</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0308</v>
+        <v>-0.9928</v>
       </c>
       <c r="E6" t="n">
-        <v>3.538</v>
+        <v>-1.6673</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.5688</v>
+        <v>0.6745</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.899</v>
+        <v>-0.8309</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9678</v>
+        <v>-0.8309</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0687</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.755</v>
+        <v>-0.8309</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7042</v>
+        <v>-0.8309</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0508</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.654</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6719</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.9821</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3887</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2589</v>
+        <v>0.5442</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5667</v>
+        <v>0.5442</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6922</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.532</v>
+        <v>1.2777</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7384</v>
+        <v>0.6032</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0542</v>
+        <v>-1.0837</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0591</v>
+        <v>3.9174</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.1133</v>
+        <v>-5.0011</v>
       </c>
       <c r="G7" t="n">
         <v>-0.438</v>
@@ -1000,13 +1000,13 @@
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0465</v>
+        <v>0.017</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1418</v>
+        <v>0.0001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0953</v>
+        <v>0.017</v>
       </c>
       <c r="V7" t="n">
         <v>-0.266</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8902</v>
+        <v>-1.8593</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0077</v>
+        <v>-2.4378</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8979</v>
+        <v>0.5785</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.4233</v>
+        <v>-2.2579</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.8931</v>
+        <v>-2.898</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5302</v>
+        <v>0.64</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.1184</v>
+        <v>-1.1512</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.5638</v>
+        <v>-1.2341</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5546</v>
+        <v>0.0829</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.305</v>
+        <v>-1.1067</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.3294</v>
+        <v>-1.6638</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9756</v>
+        <v>0.5572</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3887</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>2.579</v>
+        <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5331</v>
+        <v>-0.129</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9784</v>
+        <v>-0.0963</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5547</v>
+        <v>-0.0327</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8097</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>2.5364</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7267</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,75 +1111,71 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1436</v>
+        <v>-1.9214</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8063</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6627</v>
+        <v>-1.9856</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2579</v>
+        <v>-2.756</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.898</v>
+        <v>-1.1897</v>
       </c>
       <c r="I9" t="n">
-        <v>0.64</v>
+        <v>-1.5663</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1512</v>
+        <v>0.1208</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2341</v>
+        <v>0.0806</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0829</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1067</v>
+        <v>-2.8769</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6638</v>
+        <v>-1.2704</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5572</v>
+        <v>-1.6065</v>
       </c>
       <c r="P9" t="n">
         <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4132</v>
+        <v>0.0411</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4647</v>
+        <v>0.1417</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0515</v>
+        <v>-0.1006</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>. VICENTE SABARIEGO</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1189,13 +1185,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3179</v>
+        <v>-1.9214</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3043</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0136</v>
+        <v>-1.9856</v>
       </c>
       <c r="G10" t="n">
         <v>-2.756</v>
@@ -1234,13 +1230,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3554</v>
+        <v>0.0411</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2267</v>
+        <v>0.1417</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1287</v>
+        <v>-0.1006</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1253,7 +1249,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A. CRUZ URBANEJA</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1263,73 +1263,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3179</v>
+        <v>-2.9988</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3043</v>
+        <v>1.7509</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0136</v>
+        <v>-4.7496</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.756</v>
+        <v>-2.9033</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1897</v>
+        <v>-4.2985</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5663</v>
+        <v>1.3952</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1208</v>
+        <v>-0.5148</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0806</v>
+        <v>-2.2921</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0402</v>
+        <v>1.7773</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8769</v>
+        <v>-2.3885</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2704</v>
+        <v>-2.0064</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6065</v>
+        <v>-0.3821</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3554</v>
+        <v>-0.4761</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2267</v>
+        <v>0.2495</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1287</v>
+        <v>-0.7256</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1341,67 +1341,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9998</v>
+        <v>-3.4668</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9743000000000001</v>
+        <v>-1.092</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9741</v>
+        <v>-2.3748</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9033</v>
+        <v>-7.4233</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2985</v>
+        <v>-4.8931</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3952</v>
+        <v>-2.5302</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5148</v>
+        <v>-3.1184</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2921</v>
+        <v>-2.5638</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7773</v>
+        <v>-0.5546</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3885</v>
+        <v>-4.305</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0064</v>
+        <v>-2.3294</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3821</v>
+        <v>-1.9756</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9838</v>
+        <v>2.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4771</v>
+        <v>0.9565</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5271</v>
+        <v>0.8787</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.95</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2065</v>
+        <v>1.8097</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4129</v>
+        <v>2.5364</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.6194</v>
+        <v>-0.7267</v>
       </c>
     </row>
     <row r="13">
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.316</v>
+        <v>-4.9195</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2497</v>
+        <v>-2.8813</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0663</v>
+        <v>-2.0382</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7079</v>
@@ -1464,13 +1464,13 @@
         <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0209</v>
+        <v>0.3755</v>
       </c>
       <c r="T13" t="n">
-        <v>0.034</v>
+        <v>0.4025</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.055</v>
+        <v>-0.0269</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.984</v>
+        <v>-4.760000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3659</v>
+        <v>14.562</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.3499</v>
+        <v>-19.3217</v>
       </c>
       <c r="G14" t="n">
         <v>-15.246</v>
@@ -1512,13 +1512,13 @@
         <v>-14.3925</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.853600000000001</v>
+        <v>-0.8536000000000001</v>
       </c>
       <c r="J14" t="n">
         <v>11.8275</v>
       </c>
       <c r="K14" t="n">
-        <v>1.196700000000001</v>
+        <v>1.1967</v>
       </c>
       <c r="L14" t="n">
         <v>10.6308</v>
@@ -1542,13 +1542,13 @@
         <v>16.8625</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2418999999999994</v>
+        <v>0.9821</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8792999999999999</v>
+        <v>2.0754</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1214</v>
+        <v>-1.0931</v>
       </c>
       <c r="V14" t="n">
         <v>7.718500000000001</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.649800000000001</v>
+        <v>9.5273</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5318</v>
+        <v>8.042</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1179</v>
+        <v>1.4853</v>
       </c>
       <c r="G15" t="n">
         <v>6.3358</v>
@@ -1620,13 +1620,13 @@
         <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4127</v>
+        <v>0.4648</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8274</v>
+        <v>-0.3173</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4147</v>
+        <v>0.782</v>
       </c>
       <c r="V15" t="n">
         <v>1.9331</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.504</v>
+        <v>5.9937</v>
       </c>
       <c r="E16" t="n">
-        <v>7.0838</v>
+        <v>7.3899</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5799</v>
+        <v>-1.3962</v>
       </c>
       <c r="G16" t="n">
         <v>5.0205</v>
@@ -1698,13 +1698,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0544</v>
+        <v>0.5441</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3514</v>
+        <v>-0.0453</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4057</v>
+        <v>0.5894</v>
       </c>
       <c r="V16" t="n">
         <v>2.4129</v>
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3602</v>
+        <v>1.2761</v>
       </c>
       <c r="E17" t="n">
-        <v>2.504</v>
+        <v>2.0959</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1438</v>
+        <v>-0.8199</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2934</v>
@@ -1776,13 +1776,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3326</v>
+        <v>1.2484</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.3515</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5729</v>
+        <v>0.8969</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8692</v>
@@ -1809,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5372</v>
+        <v>1.1834</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6383</v>
+        <v>2.1484</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1011</v>
+        <v>-0.9651</v>
       </c>
       <c r="G18" t="n">
         <v>1.8797</v>
@@ -1854,13 +1854,13 @@
         <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3344</v>
+        <v>0.3118</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.238</v>
+        <v>0.2721</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0964</v>
+        <v>0.0396</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4775</v>
+        <v>0.6076</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9089</v>
+        <v>0.6028</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4314</v>
+        <v>0.0048</v>
       </c>
       <c r="G19" t="n">
         <v>3.4134</v>
@@ -1932,13 +1932,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1434</v>
+        <v>0.2735</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4535</v>
+        <v>0.1474</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3101</v>
+        <v>0.1261</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4842</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6972</v>
+        <v>-0.953</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3675</v>
+        <v>-2.2777</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0647</v>
+        <v>1.3247</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4583</v>
+        <v>-2.0994</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4433</v>
+        <v>-1.3052</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.7942</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1188</v>
+        <v>-2.2089</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9582000000000001</v>
+        <v>-1.5312</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1606</v>
+        <v>-0.6776</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5772</v>
+        <v>0.1095</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5148</v>
+        <v>0.226</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0623</v>
+        <v>-0.1165</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3644</v>
+        <v>-0.0439</v>
       </c>
       <c r="T20" t="n">
-        <v>1.7006</v>
+        <v>-0.2833</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3362</v>
+        <v>0.2394</v>
       </c>
       <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="X20" t="n">
         <v>-1.2065</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.7384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5354</v>
+        <v>-1.0908</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1756</v>
+        <v>0.4493</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6402</v>
+        <v>-1.5401</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0994</v>
+        <v>-0.4583</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3052</v>
+        <v>0.4433</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7942</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2089</v>
+        <v>1.1188</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5312</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6776</v>
+        <v>0.1606</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1095</v>
+        <v>-1.5772</v>
       </c>
       <c r="N21" t="n">
-        <v>0.226</v>
+        <v>-0.5148</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1165</v>
+        <v>-1.0623</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1903</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6263</v>
+        <v>0.9707</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1813</v>
+        <v>0.7823</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.445</v>
+        <v>0.1884</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0.532</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8592</v>
+        <v>-1.5931</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7235</v>
+        <v>1.4174</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5827</v>
+        <v>-3.0105</v>
       </c>
       <c r="G22" t="n">
         <v>2.0864</v>
@@ -2166,13 +2166,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.191</v>
+        <v>0.0751</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1304</v>
+        <v>-0.1757</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3215</v>
+        <v>0.2507</v>
       </c>
       <c r="V22" t="n">
         <v>-4.1513</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4702</v>
+        <v>-2.2381</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8711</v>
+        <v>-0.6671</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5991</v>
+        <v>-1.571</v>
       </c>
       <c r="G23" t="n">
         <v>-2.033</v>
@@ -2244,13 +2244,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4291</v>
+        <v>-0.1969</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6032</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3006</v>
+        <v>-4.9657</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3749</v>
+        <v>-1.8648</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9257</v>
+        <v>-3.101</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3617</v>
@@ -2322,13 +2322,13 @@
         <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0146</v>
+        <v>0.3202</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1416</v>
+        <v>0.3685</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.873</v>
+        <v>-0.0483</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5437</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.666100000000001</v>
+        <v>7.747400000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>17.3362</v>
+        <v>17.3361</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.6703</v>
+        <v>-9.588999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>12.49</v>
@@ -2400,19 +2400,19 @@
         <v>14.8789</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1133</v>
+        <v>3.9678</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9926999999999997</v>
+        <v>0.9924999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1062</v>
+        <v>2.9749</v>
       </c>
       <c r="V25" t="n">
         <v>-7.7186</v>
       </c>
       <c r="W25" t="n">
-        <v>8.0177</v>
+        <v>8.017700000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-15.7361</v>
